--- a/next-dashboard-ui/attendance_cctv/backend/exports/attendance_star_2026-04-13.xlsx
+++ b/next-dashboard-ui/attendance_cctv/backend/exports/attendance_star_2026-04-13.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -720,7 +720,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
